--- a/data/funds_master.xlsx
+++ b/data/funds_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harum\tsumitate-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CE62D7-37E5-4842-943B-D9E0A22A84A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9458C7CB-C502-402A-976D-EAC4B9C417ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,21 @@
     <sheet name="funds" sheetId="1" r:id="rId1"/>
     <sheet name="README" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">funds!$A$1:$H$31</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -26,6 +40,33 @@
     <author>本山真理子</author>
   </authors>
   <commentList>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{A7D830CA-E060-4323-A2D4-8F57B3F6190D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>本山真理子:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+全角の英数カナ文字は
+必ず半角に変換すること。</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H1" authorId="0" shapeId="0" xr:uid="{F5F7E7E8-2BF7-450D-9226-D68D6F5048B8}">
       <text>
         <r>
@@ -58,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="95">
   <si>
     <t>id</t>
   </si>
@@ -67,18 +108,6 @@
   </si>
   <si>
     <t>provider</t>
-  </si>
-  <si>
-    <t>emaxis-slim-all-country</t>
-  </si>
-  <si>
-    <t>eMAXIS Slim 全世界株式（オール・カントリー）</t>
-  </si>
-  <si>
-    <t>eMAXIS Slim 米国株式（S&amp;P500）</t>
-  </si>
-  <si>
-    <t>rakuten-plus-all-country</t>
   </si>
   <si>
     <t>楽天</t>
@@ -130,13 +159,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>楽天・プラス・Ｓ＆Ｐ５００インデックス・ファンド</t>
-  </si>
-  <si>
-    <t>楽天・プラス・オールカントリー株式インデックス・ファンド</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>リターン（年率）</t>
     <rPh sb="5" eb="7">
       <t>ネンリツ</t>
@@ -148,14 +170,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>楽天・全米株式インデックス・ファンド</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>iFreeNEXT FANG+インデックス</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>大和ｱｾｯﾄ</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -170,10 +184,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>楽天・全世界株式インデックス・ファンド</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>株式-為替ヘッジなし,先進国・新興国（広域）</t>
     <rPh sb="0" eb="2">
       <t>カブシキ</t>
@@ -202,27 +212,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>楽天・プラス・日経２２５インデックス・ファンド</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>たわらノーロード先進国株式</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>たわらノーロード　日経２２５</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>iFreeS&amp;P500インデックス</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>ｱｾｯﾄﾏﾈｼﾞﾒﾝﾄOne</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>【らくらく投資専用】楽天・資産づくりファンド（しっかりコース）</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -245,31 +235,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>キャピタル世界株式ファンド（ＤＣ年金つみたて専用）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>ｷｬﾋﾟﾀﾙ・ｲﾝﾀｰﾅｼｮﾅﾙ</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>eMAXIS Slimバランス(8資産均等型)</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Smart-i S&amp;P500インデックス</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>My SMT S&amp;P500インデックス(ノーロード)</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>つみたて日本株式(TOPIX)</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>SBI・全世界株式インデックス・ファンド</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -316,19 +282,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>三井住友・ＤＣつみたてＮＩＳＡ・日本株インデックスファンド</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>三井住友DS</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>日経平均高配当利回り株ファンド</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>つみたて8資産均等バランス</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -339,110 +293,355 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>emaxis-slim-sp500</t>
+  </si>
+  <si>
+    <t>rakuten-sp500</t>
+  </si>
+  <si>
+    <t>ifreenext-fangplus</t>
+  </si>
+  <si>
+    <t>ifree-sp500</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>eMAXIS Slim 全世界株式(ｵｰﾙ･ｶﾝﾄﾘｰ)</t>
+  </si>
+  <si>
+    <t>eMAXIS Slim 米国株式(S&amp;P500)</t>
+  </si>
+  <si>
+    <t>楽天･ﾌﾟﾗｽ･ｵｰﾙｶﾝﾄﾘｰ株式ｲﾝﾃﾞｯｸｽ･ﾌｧﾝﾄﾞ</t>
+  </si>
+  <si>
+    <t>楽天･ﾌﾟﾗｽ･S&amp;P500ｲﾝﾃﾞｯｸｽ･ﾌｧﾝﾄﾞ</t>
+  </si>
+  <si>
+    <t>楽天･全米株式ｲﾝﾃﾞｯｸｽ･ﾌｧﾝﾄﾞ</t>
+  </si>
+  <si>
+    <t>eMAXIS Slim 国内株式(TOPIX)</t>
+  </si>
+  <si>
+    <t>楽天･全世界株式ｲﾝﾃﾞｯｸｽ･ﾌｧﾝﾄﾞ</t>
+  </si>
+  <si>
+    <t>eMAXIS Slim 全世界株式(除く日本)</t>
+  </si>
+  <si>
+    <t>eMAXIS Slim 先進国株式ｲﾝﾃﾞｯｸｽ(除く日本)</t>
+  </si>
+  <si>
+    <t>楽天･ﾌﾟﾗｽ･日経225ｲﾝﾃﾞｯｸｽ･ﾌｧﾝﾄﾞ</t>
+  </si>
+  <si>
+    <t>eMAXIS Slim 国内株式(日経平均)</t>
+  </si>
+  <si>
+    <t>たわらﾉｰﾛｰﾄﾞ 日経225</t>
+  </si>
+  <si>
+    <t>たわらﾉｰﾛｰﾄﾞ先進国株式</t>
+  </si>
+  <si>
+    <t>eMAXIS Slim 新興国株式ｲﾝﾃﾞｯｸｽ</t>
+  </si>
+  <si>
+    <t>iFreeS&amp;P500ｲﾝﾃﾞｯｸｽ</t>
+  </si>
+  <si>
+    <t>eMAXIS Slimﾊﾞﾗﾝｽ(8資産均等型)</t>
+  </si>
+  <si>
+    <t>Smart-i S&amp;P500ｲﾝﾃﾞｯｸｽ</t>
+  </si>
+  <si>
+    <t>My SMT S&amp;P500ｲﾝﾃﾞｯｸｽ(ﾉｰﾛｰﾄﾞ)</t>
+  </si>
+  <si>
+    <t>つみたて日本株式(TOPIX)</t>
+  </si>
+  <si>
+    <t>SBI･全世界株式ｲﾝﾃﾞｯｸｽ･ﾌｧﾝﾄﾞ</t>
+  </si>
+  <si>
+    <t>日経平均高配当利回り株ﾌｧﾝﾄﾞ</t>
+  </si>
+  <si>
+    <t>つみたて8資産均等ﾊﾞﾗﾝｽ</t>
+  </si>
+  <si>
     <t>つみたて日本株式(日経平均)</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>楽天・全世界株式(除く米国)インデックス・ファンド</t>
-    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>楽天･全世界株式(除く米国)ｲﾝﾃﾞｯｸｽ･ﾌｧﾝﾄﾞ</t>
   </si>
   <si>
     <t>eMAXIS Slim 全世界株式(3地域均等型)</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>eMAXIS Slim 全世界株式（除く日本）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>eMAXIS Slim 先進国株式インデックス（除く日本）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>eMAXIS Slim 国内株式（日経平均）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>eMAXIS Slim 新興国株式インデックス</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>eMAXIS Slim 国内株式（TOPIX）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>【らくらく投資専用】楽天・資産づくりファンド（なかなかコース）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>emaxis-slim-sp500</t>
-  </si>
-  <si>
-    <t>rakuten-sp500</t>
-  </si>
-  <si>
-    <t>ifreenext-fangplus</t>
-  </si>
-  <si>
-    <t>emaxis-slim-topix</t>
-  </si>
-  <si>
-    <t>emaxis-slim</t>
-  </si>
-  <si>
-    <t>ifreesp500</t>
-  </si>
-  <si>
-    <t>emaxis-slim8</t>
+  </si>
+  <si>
+    <t>【らくらく投資専用】楽天･資産づくりﾌｧﾝﾄﾞ(なかなかｺｰｽ)</t>
+  </si>
+  <si>
+    <t>【らくらく投資専用】楽天･資産づくりﾌｧﾝﾄﾞ(しっかりｺｰｽ)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ｷｬﾋﾟﾀﾙ世界株式ﾌｧﾝﾄﾞ(DC年金つみたて専用)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>三井住友･DCつみたてNISA･日本株ｲﾝﾃﾞｯｸｽﾌｧﾝﾄﾞ</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>smart-i-sp500</t>
-  </si>
-  <si>
-    <t>my-smt-sp500</t>
-  </si>
-  <si>
-    <t>topix</t>
-  </si>
-  <si>
-    <t>sbi</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>emaxis-slim-3</t>
-  </si>
-  <si>
-    <t>rakuten-usa</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>emaxis-slim-oll-country</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>rakuten-oll-country</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>emaxis-slim-developed</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>rakuten-plus-nikkei</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>emaxis-slim-japan</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>tawara-nikkei</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>tawara-developed</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>rakuten-全米株式</t>
+    <rPh sb="8" eb="10">
+      <t>ゼンベイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カブシキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>iFreeNEXT FANG+ｲﾝﾃﾞｯｸｽ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>rakuten-全世界株式</t>
+    <rPh sb="8" eb="11">
+      <t>ゼンセカイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カブシキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>rakuten-plus-日経225</t>
+    <rPh sb="13" eb="15">
+      <t>ニッケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>tawara-日経225</t>
+    <rPh sb="7" eb="9">
+      <t>ニッケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>tawara-先進国株式</t>
+    <rPh sb="7" eb="10">
+      <t>センシンコク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カブシキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>emaxis-slim-新興国株式</t>
+    <rPh sb="12" eb="15">
+      <t>シンコウコク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カブシキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>capital-DC年金つみたて</t>
+    <rPh sb="10" eb="12">
+      <t>ネンキン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>sbi-全世界株式</t>
+    <rPh sb="4" eb="7">
+      <t>ゼンセカイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カブシキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>mitsuisumitomo-DCつみたて</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>nikkeiheikin-高配当利回り株</t>
+    <rPh sb="13" eb="16">
+      <t>コウハイトウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>リマワ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>カブ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>tsumitate-8資産均等</t>
+    <rPh sb="11" eb="13">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キントウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>rakuten-らくらく-なかなか</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>rakuten-らくらく-しっかり</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>rakuten-全世界株式-米国除く</t>
+    <rPh sb="8" eb="11">
+      <t>ゼンセカイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ベイ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>コク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ノゾ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>emaxis-slim-全世界株式-3地域均等</t>
+    <rPh sb="12" eb="15">
+      <t>ゼンセカイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>チイキ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>キントウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>tsumitate-日本株式-TOPIX</t>
+    <rPh sb="10" eb="12">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カブシキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>tsumitate-日本株式-日経</t>
+    <rPh sb="10" eb="12">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ニッケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>emaxis-slim-国内株式-TOPIX</t>
+    <rPh sb="12" eb="14">
+      <t>コクナイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カブシキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>emaxis-slim-全世界株式-除く日本</t>
+    <rPh sb="12" eb="15">
+      <t>ゼンセカイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ニホン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>emaxis-slim-先進国株式-除く日本</t>
+    <rPh sb="12" eb="15">
+      <t>センシンコク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ニホン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>emaxis-slim-国内株式-日経</t>
+    <rPh sb="12" eb="14">
+      <t>コクナイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニッケイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>emaxis-slim-8資産均等</t>
+    <rPh sb="13" eb="15">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キントウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>my-smt-sp500-ﾉｰﾛｰﾄﾞ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>emaxis-slim-ｵﾙｶﾝ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>rakuten-plus-ｵﾙｶﾝ</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -546,7 +745,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -574,15 +773,19 @@
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -904,7 +1107,7 @@
   <cols>
     <col min="1" max="1" width="8.88671875" style="9"/>
     <col min="2" max="2" width="26" style="9" customWidth="1"/>
-    <col min="3" max="3" width="44" style="9" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" style="10" customWidth="1"/>
     <col min="4" max="4" width="14" style="9" customWidth="1"/>
     <col min="5" max="5" width="14" style="6" customWidth="1"/>
     <col min="6" max="6" width="34" style="10" customWidth="1"/>
@@ -924,36 +1127,36 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.4">
       <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>4</v>
+      <c r="B2" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6">
         <v>98839.62</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G2" s="11">
         <v>5.7749999999999998E-3</v>
@@ -966,20 +1169,20 @@
       <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>5</v>
+      <c r="B3" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E3" s="6">
         <v>99666.02</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G3" s="11">
         <v>8.1400000000000005E-4</v>
@@ -992,20 +1195,20 @@
       <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>20</v>
+      <c r="B4" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E4" s="6">
         <v>6857.06</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G4" s="11">
         <v>5.6099999999999998E-4</v>
@@ -1018,20 +1221,20 @@
       <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>19</v>
+      <c r="B5" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E5" s="7">
         <v>8773.2099999999991</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G5" s="11">
         <v>7.6999999999999996E-4</v>
@@ -1044,20 +1247,20 @@
       <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>23</v>
+      <c r="B6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E6" s="7">
         <v>22298.19</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G6" s="11">
         <v>1.6199999999999999E-3</v>
@@ -1070,20 +1273,20 @@
       <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>24</v>
+      <c r="B7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E7" s="7">
         <v>9272.48</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G7" s="11">
         <v>7.7549999999999997E-3</v>
@@ -1096,20 +1299,20 @@
       <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>65</v>
+      <c r="B8" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E8" s="7">
         <v>5823.46</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G8" s="11">
         <v>1.4300000000000001E-3</v>
@@ -1122,20 +1325,20 @@
       <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>27</v>
+      <c r="B9" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E9" s="7">
         <v>7776.68</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G9" s="11">
         <v>1.7899999999999999E-3</v>
@@ -1148,20 +1351,20 @@
       <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>61</v>
+      <c r="B10" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" s="7">
         <v>9809.75</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G10" s="11">
         <v>5.775E-4</v>
@@ -1174,20 +1377,20 @@
       <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>62</v>
+      <c r="B11" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E11" s="7">
         <v>11514.64</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="G11" s="11">
         <v>9.8890000000000002E-4</v>
@@ -1200,20 +1403,20 @@
       <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>32</v>
+      <c r="B12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E12" s="7">
         <v>619.71</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G12" s="11">
         <v>1.32E-3</v>
@@ -1226,20 +1429,20 @@
       <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>63</v>
+      <c r="B13" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E13" s="7">
         <v>3238.82</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G13" s="11">
         <v>1.4300000000000001E-3</v>
@@ -1252,20 +1455,20 @@
       <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>34</v>
+      <c r="B14" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E14" s="7">
         <v>3585.12</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G14" s="11">
         <v>1.4300000000000001E-3</v>
@@ -1278,20 +1481,20 @@
       <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>33</v>
+      <c r="B15" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E15" s="7">
         <v>10906.29</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="G15" s="11">
         <v>9.8890000000000002E-4</v>
@@ -1304,20 +1507,20 @@
       <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>64</v>
+      <c r="B16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E16" s="7">
         <v>3327.55</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G16" s="11">
         <v>1.518E-3</v>
@@ -1330,20 +1533,20 @@
       <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>35</v>
+      <c r="B17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E17" s="7">
         <v>6239.22</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G17" s="11">
         <v>1.98E-3</v>
@@ -1356,18 +1559,20 @@
       <c r="A18" s="9">
         <v>17</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="13" t="s">
-        <v>37</v>
+      <c r="B18" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E18" s="7">
         <v>769.38</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G18" s="11">
         <v>4.9150000000000001E-3</v>
@@ -1376,22 +1581,24 @@
         <v>0.1328</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="26.4">
+    <row r="19" spans="1:8">
       <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="13" t="s">
-        <v>39</v>
+      <c r="B19" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E19" s="7">
         <v>2368.94</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="G19" s="11">
         <v>1.085E-2</v>
@@ -1404,20 +1611,20 @@
       <c r="A20" s="9">
         <v>19</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>41</v>
+      <c r="B20" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E20" s="7">
         <v>4725.1099999999997</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G20" s="11">
         <v>1.4300000000000001E-3</v>
@@ -1430,20 +1637,20 @@
       <c r="A21" s="9">
         <v>20</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>42</v>
+      <c r="B21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="E21" s="7">
         <v>1019.28</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G21" s="11">
         <v>2.4199999999999998E-3</v>
@@ -1456,20 +1663,20 @@
       <c r="A22" s="9">
         <v>21</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>43</v>
+      <c r="B22" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="E22" s="7">
         <v>1379.02</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G22" s="11">
         <v>9.68E-4</v>
@@ -1482,20 +1689,20 @@
       <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>44</v>
+      <c r="B23" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>57</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E23" s="9">
         <v>857.49</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G23" s="11">
         <v>1.98E-3</v>
@@ -1508,20 +1715,20 @@
       <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>45</v>
+      <c r="C24" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E24" s="7">
         <v>3577.66</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G24" s="11">
         <v>1.0219999999999999E-3</v>
@@ -1534,18 +1741,20 @@
       <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="14"/>
+      <c r="B25" s="13" t="s">
+        <v>78</v>
+      </c>
       <c r="C25" s="10" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E25" s="7">
         <v>2462.1799999999998</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G25" s="11">
         <v>1.7600000000000001E-3</v>
@@ -1558,18 +1767,20 @@
       <c r="A26" s="9">
         <v>25</v>
       </c>
-      <c r="B26" s="14"/>
+      <c r="B26" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C26" s="10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E26" s="7">
         <v>2688.39</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G26" s="11">
         <v>6.9300000000000004E-3</v>
@@ -1582,20 +1793,20 @@
       <c r="A27" s="9">
         <v>26</v>
       </c>
-      <c r="B27" s="14" t="s">
-        <v>78</v>
+      <c r="B27" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E27" s="7">
         <v>2406.5500000000002</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="G27" s="11">
         <v>2.4199999999999998E-3</v>
@@ -1608,18 +1819,20 @@
       <c r="A28" s="9">
         <v>27</v>
       </c>
-      <c r="B28" s="14"/>
+      <c r="B28" s="13" t="s">
+        <v>86</v>
+      </c>
       <c r="C28" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E28" s="7">
         <v>2595.77</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G28" s="11">
         <v>1.98E-3</v>
@@ -1632,18 +1845,20 @@
       <c r="A29" s="9">
         <v>28</v>
       </c>
-      <c r="B29" s="14"/>
+      <c r="B29" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="C29" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E29" s="7">
         <v>213.56</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G29" s="11">
         <v>1.82E-3</v>
@@ -1656,20 +1871,20 @@
       <c r="A30" s="9">
         <v>29</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>79</v>
+      <c r="B30" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E30" s="7">
         <v>417.22</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="G30" s="11">
         <v>5.775E-4</v>
@@ -1682,18 +1897,20 @@
       <c r="A31" s="9">
         <v>30</v>
       </c>
-      <c r="B31" s="14"/>
+      <c r="B31" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="C31" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E31" s="7">
         <v>529.57000000000005</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G31" s="11">
         <v>4.9150000000000001E-3</v>
@@ -1703,12 +1920,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="B2:B31">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C100">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
@@ -1725,37 +1943,37 @@
   <sheetData>
     <row r="1" spans="1:1" ht="16.2">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/funds_master.xlsx
+++ b/data/funds_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harum\tsumitate-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCEE7A7A-73BD-424C-9068-C9B70A2D0B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A236AF4-BB64-4F65-8755-D2D0DCA5BE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -224,9 +224,6 @@
     <t>eMAXIS Slim 国内株式(日経平均)</t>
   </si>
   <si>
-    <t>eMAXIS Slim 新興国株式ｲﾝﾃﾞｯｸｽ</t>
-  </si>
-  <si>
     <t>eMAXIS Slimﾊﾞﾗﾝｽ(8資産均等型)</t>
   </si>
   <si>
@@ -669,6 +666,10 @@
     <rPh sb="2" eb="4">
       <t>トウシン</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>eMAXIS Slim 新興国株式ｲﾝﾃﾞｯｸｽ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -746,7 +747,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -756,6 +757,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -772,7 +779,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -788,6 +795,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1112,7 +1123,7 @@
   <cols>
     <col min="1" max="1" width="3.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="49.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="3" customWidth="1"/>
     <col min="5" max="5" width="9.44140625" style="3" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" style="3" customWidth="1"/>
@@ -1125,10 +1136,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="4" customFormat="1" ht="26.4">
       <c r="A1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1137,22 +1148,22 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.8">
@@ -1160,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>21</v>
@@ -1169,19 +1180,19 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="9">
         <v>5.775E-4</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.8">
@@ -1189,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>22</v>
@@ -1198,19 +1209,19 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="9">
         <v>8.1400000000000005E-4</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.8">
@@ -1218,28 +1229,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="9">
         <v>5.6099999999999998E-4</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16.8">
@@ -1247,28 +1258,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="9">
         <v>7.6999999999999996E-4</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16.8">
@@ -1276,28 +1287,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="9">
         <v>1.6199999999999999E-3</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="16.8">
@@ -1305,28 +1316,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="9">
         <v>7.7549999999999997E-3</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="16.8">
@@ -1334,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>23</v>
@@ -1343,19 +1354,19 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="9">
         <v>1.4300000000000001E-3</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="16.8">
@@ -1363,28 +1374,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>59</v>
+        <v>106</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="9">
         <v>1.7899999999999999E-3</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="16.8">
@@ -1392,7 +1403,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>24</v>
@@ -1401,19 +1412,19 @@
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="9">
         <v>5.775E-4</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.8">
@@ -1421,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>25</v>
@@ -1430,19 +1441,19 @@
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="9">
         <v>9.8890000000000002E-4</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16.8">
@@ -1450,28 +1461,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="9">
         <v>1.32E-3</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16.8">
@@ -1479,7 +1490,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>26</v>
@@ -1488,19 +1499,19 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="9">
         <v>1.4300000000000001E-3</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="16.8">
@@ -1508,28 +1519,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="9">
         <v>1.4300000000000001E-3</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.8">
@@ -1537,28 +1548,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="9">
         <v>9.8890000000000002E-4</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.8">
@@ -1566,28 +1577,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="9">
         <v>1.518E-3</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.8">
@@ -1595,28 +1606,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="9">
         <v>1.98E-3</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="28.8">
@@ -1624,31 +1635,31 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="9">
         <v>4.9150000000000001E-3</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="16.8">
@@ -1656,28 +1667,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="9">
         <v>1.085E-2</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.8">
@@ -1685,28 +1696,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="9">
         <v>1.4300000000000001E-3</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.8">
@@ -1714,28 +1725,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="9">
         <v>2.4199999999999998E-3</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.8">
@@ -1743,28 +1754,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="9">
         <v>9.68E-4</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.8">
@@ -1772,28 +1783,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="9">
         <v>1.98E-3</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.8">
@@ -1801,28 +1812,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="9">
         <v>1.0219999999999999E-3</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.8">
@@ -1830,28 +1841,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="9">
         <v>1.7600000000000001E-3</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="16.8">
@@ -1859,28 +1870,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="9">
         <v>6.9300000000000004E-3</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="16.8">
@@ -1888,28 +1899,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="9">
         <v>2.4199999999999998E-3</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.8">
@@ -1917,28 +1928,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="9">
         <v>1.98E-3</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.8">
@@ -1946,28 +1957,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="9">
         <v>1.82E-3</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.8">
@@ -1975,28 +1986,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="9">
         <v>5.775E-4</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="28.8">
@@ -2004,31 +2015,31 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="9">
         <v>4.9150000000000001E-3</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/funds_master.xlsx
+++ b/data/funds_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harum\tsumitate-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A236AF4-BB64-4F65-8755-D2D0DCA5BE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FE1B52-56BC-4C92-944F-9F642D56C437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="funds" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">funds!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">funds!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="148">
   <si>
     <t>name</t>
   </si>
@@ -250,16 +250,6 @@
   </si>
   <si>
     <t>https://emaxis.am.mufg.jp/fund/253425.html</t>
-  </si>
-  <si>
-    <t>CSV取得先サイト</t>
-    <rPh sb="3" eb="5">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>https://emaxis.am.mufg.jp/fund/253266.html</t>
@@ -654,10 +644,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>expense_ratio</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>sbi_total_world</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -670,6 +656,84 @@
   </si>
   <si>
     <t>eMAXIS Slim 新興国株式ｲﾝﾃﾞｯｸｽ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>設定来データCSV取得先サイト</t>
+    <rPh sb="0" eb="3">
+      <t>セッテイライ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>expense_source_type</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>expense_fetch_method</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>expense_enabled</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>expense_source_url</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.rakuten-toushin.co.jp/fund/nav/riracwi/pdf/riracwi_P.pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>rakuten_pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.rakuten-toushin.co.jp/fund/nav/rirsp500/pdf/rirsp500_P.pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.rakuten-toushin.co.jp/fund/nav/rivue/pdf/rivue_P.pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.rakuten-toushin.co.jp/fund/nav/rivge/pdf/rivge_P.pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.rakuten-toushin.co.jp/fund/nav/riabf/pdf/riabf_P.pdf</t>
+  </si>
+  <si>
+    <t>https://www.rakuten-toushin.co.jp/fund/nav/riabf/pdf/riabf_P.pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.rakuten-toushin.co.jp/fund/nav/rivgexu/pdf/rivgexu_P.pdf</t>
+  </si>
+  <si>
+    <t>https://www.rakuten-toushin.co.jp/fund/nav/rirn225/pdf/rirn225_P.pdf</t>
+  </si>
+  <si>
+    <t>https://www.sbiam.co.jp/fund/memo/sa_2017120601.html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>sbi_html</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -677,10 +741,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00000%"/>
-  </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,8 +807,32 @@
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -761,7 +846,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -779,32 +870,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1117,29 +1220,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:J31"/>
+  <sheetPr codeName="Sheet2" filterMode="1"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="41.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="3.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" style="2" customWidth="1"/>
+    <col min="8" max="9" width="17.44140625" style="3" customWidth="1"/>
+    <col min="10" max="12" width="16" style="10" customWidth="1"/>
+    <col min="13" max="13" width="42" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" ht="26.4">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="26.4">
+      <c r="A1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1148,941 +1251,1110 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="42" hidden="1">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="42" hidden="1">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="68.400000000000006">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L4" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="68.400000000000006">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L5" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="68.400000000000006">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L6" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="68.400000000000006" hidden="1">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="42" hidden="1">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="68.400000000000006">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L9" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="42" hidden="1">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="42" hidden="1">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="68.400000000000006">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L12" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="42" hidden="1">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="55.2" hidden="1">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" s="8"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="55.2" hidden="1">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="8"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="42" hidden="1">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="68.400000000000006" hidden="1">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="68.400000000000006">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L18" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="55.2" hidden="1">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="8"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="42" hidden="1">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20" s="8"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="55.2" hidden="1">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="8"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="42" hidden="1">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="8"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="42" hidden="1">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="8"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="68.400000000000006">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
         <v>127</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="C24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="L24" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="42" hidden="1">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I25" s="8"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="42" hidden="1">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="42" hidden="1">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I27" s="8"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="42" hidden="1">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="I28" s="8"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="68.400000000000006">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="E29" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L29" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="42" hidden="1">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>113</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="8"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="68.400000000000006">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L31" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.8">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="9">
-        <v>5.775E-4</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="16.8">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="9">
-        <v>8.1400000000000005E-4</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="16.8">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="9">
-        <v>5.6099999999999998E-4</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="16.8">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="9">
-        <v>7.6999999999999996E-4</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="16.8">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="9">
-        <v>1.6199999999999999E-3</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16.8">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="9">
-        <v>7.7549999999999997E-3</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.8">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="9">
-        <v>1.4300000000000001E-3</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16.8">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="9">
-        <v>1.7899999999999999E-3</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16.8">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="9">
-        <v>5.775E-4</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="16.8">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>114</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="9">
-        <v>9.8890000000000002E-4</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="16.8">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="9">
-        <v>1.32E-3</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="16.8">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>114</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" s="9">
-        <v>1.4300000000000001E-3</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="16.8">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="9">
-        <v>1.4300000000000001E-3</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="16.8">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="9">
-        <v>9.8890000000000002E-4</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="16.8">
-      <c r="A16" s="3">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E16" t="s">
-        <v>114</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="9">
-        <v>1.518E-3</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="16.8">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="9">
-        <v>1.98E-3</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="28.8">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="9">
-        <v>4.9150000000000001E-3</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="16.8">
-      <c r="A19" s="3">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="9">
-        <v>1.085E-2</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="16.8">
-      <c r="A20" s="3">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>114</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="9">
-        <v>1.4300000000000001E-3</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="16.8">
-      <c r="A21" s="3">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="9">
-        <v>2.4199999999999998E-3</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="16.8">
-      <c r="A22" s="3">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="9">
-        <v>9.68E-4</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="16.8">
-      <c r="A23" s="3">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" t="s">
-        <v>114</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="9">
-        <v>1.98E-3</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="16.8">
-      <c r="A24" s="3">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="9">
-        <v>1.0219999999999999E-3</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="16.8">
-      <c r="A25" s="3">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="9">
-        <v>1.7600000000000001E-3</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="16.8">
-      <c r="A26" s="3">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26" s="9">
-        <v>6.9300000000000004E-3</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="16.8">
-      <c r="A27" s="3">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="9">
-        <v>2.4199999999999998E-3</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="16.8">
-      <c r="A28" s="3">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" t="s">
-        <v>114</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G28" s="9">
-        <v>1.98E-3</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="16.8">
-      <c r="A29" s="3">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="9">
-        <v>1.82E-3</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="16.8">
-      <c r="A30" s="3">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" s="9">
-        <v>5.775E-4</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="28.8">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="9">
-        <v>4.9150000000000001E-3</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G31" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F31" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="rakuten"/>
+        <filter val="sbi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C2:C100">
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H100">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I100">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1" xr:uid="{174F42D3-A207-49FC-A632-F883A03DB0F7}"/>
-    <hyperlink ref="I11" r:id="rId2" xr:uid="{F0720759-8E9B-4F7B-8A64-5716AE43E7A4}"/>
-    <hyperlink ref="I8" r:id="rId3" xr:uid="{C114E24E-3B3D-48B0-8CB3-8B9EAB4FB1F4}"/>
-    <hyperlink ref="I10" r:id="rId4" xr:uid="{01203336-66DE-4FBE-BB29-DA3C3E82C840}"/>
-    <hyperlink ref="I20" r:id="rId5" xr:uid="{952EC32F-2D05-4C26-8C21-E55065D06DE0}"/>
-    <hyperlink ref="I16" r:id="rId6" xr:uid="{BABF690B-C5A2-4750-9309-4F8D2A2D2A69}"/>
-    <hyperlink ref="I13" r:id="rId7" xr:uid="{EA21648D-DE13-4C8C-9F19-620024E18016}"/>
-    <hyperlink ref="I30" r:id="rId8" xr:uid="{6D4DE8B2-8D45-4158-9F3F-19830395274A}"/>
-    <hyperlink ref="I23" r:id="rId9" xr:uid="{3CDA4EBB-1365-4697-A106-40D0E059A5CC}"/>
-    <hyperlink ref="I28" r:id="rId10" xr:uid="{ADE5AED7-B1D0-41FE-B0AF-D0A680C63612}"/>
-    <hyperlink ref="I27" r:id="rId11" xr:uid="{98922A7F-2776-4EA0-8369-0102064977E7}"/>
-    <hyperlink ref="I26" r:id="rId12" xr:uid="{1A94CB07-D01D-4498-A250-F30C78F676FA}"/>
-    <hyperlink ref="I4" r:id="rId13" xr:uid="{0C243265-6C6D-4B00-ADED-674EE96112C7}"/>
-    <hyperlink ref="I5" r:id="rId14" xr:uid="{CF8DC993-3BBA-417F-886A-32C4896070FC}"/>
-    <hyperlink ref="I6" r:id="rId15" xr:uid="{461E1B74-46C7-4751-9362-BFB535A8B7B3}"/>
-    <hyperlink ref="I9" r:id="rId16" xr:uid="{18374491-91C1-4E8E-82CA-E6DDDD5C2302}"/>
-    <hyperlink ref="I12" r:id="rId17" xr:uid="{69167C07-475F-43DF-8071-FA30FEDA1295}"/>
-    <hyperlink ref="I29" r:id="rId18" xr:uid="{C0883F9E-7089-492A-B367-2C0F0969E58F}"/>
-    <hyperlink ref="I18" r:id="rId19" xr:uid="{44D4199B-375F-4D0E-A6C9-A623E20CBA9B}"/>
-    <hyperlink ref="I31" r:id="rId20" xr:uid="{C6BFF5E9-70EF-4C3C-8D9A-D046433B6195}"/>
-    <hyperlink ref="I24" r:id="rId21" xr:uid="{A343AF16-0CE5-46B6-AD52-DD53F3098137}"/>
-    <hyperlink ref="I14" r:id="rId22" xr:uid="{A122E14B-23CC-4AC9-AE43-7D0BC0BD5494}"/>
-    <hyperlink ref="I15" r:id="rId23" xr:uid="{2330DFFB-3FDC-4204-B0E2-793762DBD46B}"/>
-    <hyperlink ref="I7" r:id="rId24" xr:uid="{8B8B24FE-0245-4C9F-80AD-0C289E68A41C}"/>
-    <hyperlink ref="I17" r:id="rId25" xr:uid="{646DBE69-653A-4AD6-B790-73E119341613}"/>
-    <hyperlink ref="I21" r:id="rId26" xr:uid="{9832B1BC-B604-48DC-95C4-749F93316363}"/>
-    <hyperlink ref="I19" r:id="rId27" xr:uid="{99AADB48-BE6B-403C-A213-F8CE020BD60B}"/>
-    <hyperlink ref="I22" r:id="rId28" xr:uid="{E846061C-FFE3-4F40-BCCA-0E24F117C521}"/>
-    <hyperlink ref="I25" r:id="rId29" xr:uid="{D07D3377-957B-4264-B4CC-FD9392A99113}"/>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{174F42D3-A207-49FC-A632-F883A03DB0F7}"/>
+    <hyperlink ref="H11" r:id="rId2" xr:uid="{F0720759-8E9B-4F7B-8A64-5716AE43E7A4}"/>
+    <hyperlink ref="H8" r:id="rId3" xr:uid="{C114E24E-3B3D-48B0-8CB3-8B9EAB4FB1F4}"/>
+    <hyperlink ref="H10" r:id="rId4" xr:uid="{01203336-66DE-4FBE-BB29-DA3C3E82C840}"/>
+    <hyperlink ref="H20" r:id="rId5" xr:uid="{952EC32F-2D05-4C26-8C21-E55065D06DE0}"/>
+    <hyperlink ref="H16" r:id="rId6" xr:uid="{BABF690B-C5A2-4750-9309-4F8D2A2D2A69}"/>
+    <hyperlink ref="H13" r:id="rId7" xr:uid="{EA21648D-DE13-4C8C-9F19-620024E18016}"/>
+    <hyperlink ref="H30" r:id="rId8" xr:uid="{6D4DE8B2-8D45-4158-9F3F-19830395274A}"/>
+    <hyperlink ref="H23" r:id="rId9" xr:uid="{3CDA4EBB-1365-4697-A106-40D0E059A5CC}"/>
+    <hyperlink ref="H28" r:id="rId10" xr:uid="{ADE5AED7-B1D0-41FE-B0AF-D0A680C63612}"/>
+    <hyperlink ref="H27" r:id="rId11" xr:uid="{98922A7F-2776-4EA0-8369-0102064977E7}"/>
+    <hyperlink ref="H26" r:id="rId12" xr:uid="{1A94CB07-D01D-4498-A250-F30C78F676FA}"/>
+    <hyperlink ref="H4" r:id="rId13" xr:uid="{0C243265-6C6D-4B00-ADED-674EE96112C7}"/>
+    <hyperlink ref="H5" r:id="rId14" xr:uid="{CF8DC993-3BBA-417F-886A-32C4896070FC}"/>
+    <hyperlink ref="H6" r:id="rId15" xr:uid="{461E1B74-46C7-4751-9362-BFB535A8B7B3}"/>
+    <hyperlink ref="H9" r:id="rId16" xr:uid="{18374491-91C1-4E8E-82CA-E6DDDD5C2302}"/>
+    <hyperlink ref="H12" r:id="rId17" xr:uid="{69167C07-475F-43DF-8071-FA30FEDA1295}"/>
+    <hyperlink ref="H29" r:id="rId18" xr:uid="{C0883F9E-7089-492A-B367-2C0F0969E58F}"/>
+    <hyperlink ref="H18" r:id="rId19" xr:uid="{44D4199B-375F-4D0E-A6C9-A623E20CBA9B}"/>
+    <hyperlink ref="H31" r:id="rId20" xr:uid="{C6BFF5E9-70EF-4C3C-8D9A-D046433B6195}"/>
+    <hyperlink ref="H24" r:id="rId21" xr:uid="{A343AF16-0CE5-46B6-AD52-DD53F3098137}"/>
+    <hyperlink ref="H14" r:id="rId22" xr:uid="{A122E14B-23CC-4AC9-AE43-7D0BC0BD5494}"/>
+    <hyperlink ref="H15" r:id="rId23" xr:uid="{2330DFFB-3FDC-4204-B0E2-793762DBD46B}"/>
+    <hyperlink ref="H7" r:id="rId24" xr:uid="{8B8B24FE-0245-4C9F-80AD-0C289E68A41C}"/>
+    <hyperlink ref="H17" r:id="rId25" xr:uid="{646DBE69-653A-4AD6-B790-73E119341613}"/>
+    <hyperlink ref="H21" r:id="rId26" xr:uid="{9832B1BC-B604-48DC-95C4-749F93316363}"/>
+    <hyperlink ref="H19" r:id="rId27" xr:uid="{99AADB48-BE6B-403C-A213-F8CE020BD60B}"/>
+    <hyperlink ref="H22" r:id="rId28" xr:uid="{E846061C-FFE3-4F40-BCCA-0E24F117C521}"/>
+    <hyperlink ref="H25" r:id="rId29" xr:uid="{D07D3377-957B-4264-B4CC-FD9392A99113}"/>
+    <hyperlink ref="I4" r:id="rId30" xr:uid="{8D5DF6B2-DF56-4223-9856-DC52D4532AC2}"/>
+    <hyperlink ref="I5" r:id="rId31" xr:uid="{8B0D047A-DB25-4FFD-847C-C0175BB46677}"/>
+    <hyperlink ref="I6" r:id="rId32" xr:uid="{FD7AD871-57D7-4D8F-95A4-58DCE97F5499}"/>
+    <hyperlink ref="I9" r:id="rId33" xr:uid="{132E7635-83AB-4D18-96EF-0AEE19AF2A5E}"/>
+    <hyperlink ref="I18" r:id="rId34" xr:uid="{FA09C34B-3A76-4C4A-8A35-DF35AE1A9520}"/>
+    <hyperlink ref="I24" r:id="rId35" xr:uid="{9D123EAE-F080-46A2-9571-B6314AC7EC6C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId30"/>
+  <legacyDrawing r:id="rId36"/>
 </worksheet>
 </file>
--- a/data/funds_master.xlsx
+++ b/data/funds_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harum\tsumitate-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FE1B52-56BC-4C92-944F-9F642D56C437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4674585D-F775-4F02-AAAD-D11FED47ACB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="165">
   <si>
     <t>name</t>
   </si>
@@ -206,9 +206,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>eMAXIS Slim 全世界株式(ｵｰﾙ･ｶﾝﾄﾘｰ)</t>
-  </si>
-  <si>
     <t>eMAXIS Slim 米国株式(S&amp;P500)</t>
   </si>
   <si>
@@ -247,9 +244,6 @@
   <si>
     <t>iFreeNEXT FANG+ｲﾝﾃﾞｯｸｽ</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://emaxis.am.mufg.jp/fund/253425.html</t>
   </si>
   <si>
     <t>https://emaxis.am.mufg.jp/fund/253266.html</t>
@@ -734,6 +728,82 @@
   </si>
   <si>
     <t>sbi_html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mufg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>eMAXIS Slim 全世界株式(ｵｰﾙ･ｶﾝﾄﾘｰ)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://emaxis.am.mufg.jp/fund/253425.html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mufg_pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F253266%2F253266_20260124.pdf&amp;_gl=1*1xibmvk*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDYzMDIkajE4JGwwJGgw#page=9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F252634%2F252634_20260124.pdf&amp;_gl=1*2f99fr*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDY0NTIkajMzJGwwJGgw#page=8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F253209%2F253209_20260124.pdf&amp;_gl=1*1dhqy4k*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDY1MDEkajU0JGwwJGgw#page=10</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F252653%2F252653_20260124.pdf&amp;_gl=1*w222bc*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDY1OTEkajQ0JGwwJGgw#page=9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F253144%2F253144_20260124.pdf&amp;_gl=1*195cd7g*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDY2NDMkajUzJGwwJGgw#page=8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F252878%2F252878_20260124.pdf&amp;_gl=1*3fubfq*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDY2ODgkajgkbDAkaDA.#page=10</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F252760%2F252760_20260124.pdf&amp;_gl=1*pkw2z*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDY4NDUkajU1JGwwJGgw#page=11</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F252883%2F252883_20260325.pdf#page=8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F253425%2F253425_20260124.pdf&amp;_gl=1*1x4ohrw*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDY5MjIkajU4JGwwJGgw#page=11</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F253439%2F253439_20260314.pdf#page=10</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F252915%2F252915_20260325.pdf#page=11</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F252929%2F252929_20260325.pdf#page=8</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am.mufg.jp/viewer.html?file=%2Fpdf%2Fkoumokuromi%2F253214%2F253214_20260124.pdf&amp;_gl=1*bp1eas*_gcl_au*MTcwNjEwNjUwNi4xNzczMzgyNTQ0*_ga*NDMxMDM4NDA5LjE3NzMzODI1NDU.*_ga_3ZNV996Y9H*czE3NzQ0MDYyNjAkbzYkZzEkdDE3NzQ0MDcwNjQkajU4JGwwJGgw#page=10</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>smt_pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.smtam.jp/fund/pdf/_id_510195_type_k.pdf#page=10</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -870,7 +940,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -895,6 +965,8 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1239,10 +1311,10 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" ht="26.4">
       <c r="A1" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1251,31 +1323,31 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>133</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="42" hidden="1">
@@ -1283,31 +1355,37 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" t="b">
-        <v>0</v>
+        <v>148</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L2" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="42" hidden="1">
@@ -1315,31 +1393,37 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" t="b">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" t="s">
+        <v>149</v>
+      </c>
+      <c r="L3" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="68.400000000000006">
@@ -1347,34 +1431,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I4" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="J4" s="11" t="s">
-        <v>137</v>
-      </c>
       <c r="K4" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L4" s="11" t="b">
         <v>1</v>
@@ -1385,34 +1469,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L5" s="11" t="b">
         <v>1</v>
@@ -1423,34 +1507,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L6" s="11" t="b">
         <v>1</v>
@@ -1461,25 +1545,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="11"/>
@@ -1493,31 +1577,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" t="b">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" t="s">
+        <v>149</v>
+      </c>
+      <c r="L8" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="68.400000000000006">
@@ -1525,34 +1615,34 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L9" s="11" t="b">
         <v>1</v>
@@ -1563,31 +1653,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" t="b">
-        <v>0</v>
+        <v>36</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K10" t="s">
+        <v>149</v>
+      </c>
+      <c r="L10" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="42" hidden="1">
@@ -1595,31 +1691,37 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" t="b">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K11" t="s">
+        <v>149</v>
+      </c>
+      <c r="L11" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="68.400000000000006">
@@ -1627,34 +1729,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L12" s="11" t="b">
         <v>1</v>
@@ -1665,31 +1767,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" t="b">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" t="s">
+        <v>149</v>
+      </c>
+      <c r="L13" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="55.2" hidden="1">
@@ -1697,25 +1805,25 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I14" s="8"/>
       <c r="J14" s="11"/>
@@ -1729,25 +1837,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I15" s="8"/>
       <c r="J15" s="11"/>
@@ -1761,31 +1869,37 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" t="b">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K16" t="s">
+        <v>149</v>
+      </c>
+      <c r="L16" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="68.400000000000006" hidden="1">
@@ -1793,25 +1907,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I17" s="8"/>
       <c r="J17" s="11"/>
@@ -1825,40 +1939,40 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L18" s="11" t="b">
         <v>1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="55.2" hidden="1">
@@ -1866,25 +1980,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="11"/>
@@ -1898,31 +2012,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" t="b">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K20" t="s">
+        <v>149</v>
+      </c>
+      <c r="L20" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="55.2" hidden="1">
@@ -1930,25 +2050,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="11"/>
@@ -1957,36 +2077,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="42" hidden="1">
+    <row r="22" spans="1:13" ht="55.2">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" t="b">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="L22" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="42" hidden="1">
@@ -1994,31 +2120,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" t="b">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" t="s">
+        <v>149</v>
+      </c>
+      <c r="L23" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="68.400000000000006">
@@ -2026,34 +2158,34 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I24" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="K24" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>147</v>
       </c>
       <c r="L24" s="11" t="b">
         <v>1</v>
@@ -2064,25 +2196,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="11"/>
@@ -2096,31 +2228,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" t="b">
-        <v>0</v>
+        <v>48</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" t="s">
+        <v>149</v>
+      </c>
+      <c r="L26" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="42" hidden="1">
@@ -2128,31 +2266,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" t="b">
-        <v>0</v>
+        <v>46</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K27" t="s">
+        <v>149</v>
+      </c>
+      <c r="L27" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="42" hidden="1">
@@ -2160,31 +2304,37 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" t="b">
-        <v>0</v>
+        <v>44</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" t="s">
+        <v>149</v>
+      </c>
+      <c r="L28" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="68.400000000000006">
@@ -2192,34 +2342,34 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L29" s="11" t="b">
         <v>1</v>
@@ -2230,31 +2380,37 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I30" s="8"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" t="b">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K30" t="s">
+        <v>149</v>
+      </c>
+      <c r="L30" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="68.400000000000006">
@@ -2262,40 +2418,40 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L31" s="11" t="b">
         <v>1</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2304,6 +2460,7 @@
       <filters>
         <filter val="rakuten"/>
         <filter val="sbi"/>
+        <filter val="smt"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2314,7 +2471,7 @@
   <conditionalFormatting sqref="H2:H100">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I100">
+  <conditionalFormatting sqref="I2:I15 I17:I19 I21:I100">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
@@ -2353,8 +2510,23 @@
     <hyperlink ref="I9" r:id="rId33" xr:uid="{132E7635-83AB-4D18-96EF-0AEE19AF2A5E}"/>
     <hyperlink ref="I18" r:id="rId34" xr:uid="{FA09C34B-3A76-4C4A-8A35-DF35AE1A9520}"/>
     <hyperlink ref="I24" r:id="rId35" xr:uid="{9D123EAE-F080-46A2-9571-B6314AC7EC6C}"/>
+    <hyperlink ref="H2" r:id="rId36" xr:uid="{B123D0A4-A212-46BE-9551-9E76AA7E55A3}"/>
+    <hyperlink ref="I2" r:id="rId37" location="page=11" xr:uid="{6C1F8614-B0B3-407A-9522-A9F98C156CD0}"/>
+    <hyperlink ref="I3" r:id="rId38" location="page=9" xr:uid="{36065F43-90BF-4D72-9646-238D1D01E6E7}"/>
+    <hyperlink ref="I8" r:id="rId39" location="page=8" xr:uid="{2B48E4DC-1F73-4C9C-A32A-B46B7665E90F}"/>
+    <hyperlink ref="I10" r:id="rId40" location="page=10" xr:uid="{1EA85F97-CCF8-4FEB-AFF0-B64C4C98B3CA}"/>
+    <hyperlink ref="I11" r:id="rId41" location="page=9" xr:uid="{D62B33C9-74D7-45E2-B677-2C3559219534}"/>
+    <hyperlink ref="I13" r:id="rId42" location="page=8" xr:uid="{202DF867-DC82-4142-9C4C-B99F3B0F0A56}"/>
+    <hyperlink ref="I16" r:id="rId43" location="page=10" xr:uid="{767CC3C4-1E1A-4257-8A33-D135DE0706E9}"/>
+    <hyperlink ref="I20" r:id="rId44" location="page=11" xr:uid="{F4C4A93A-B23B-4B67-9809-9B768E31051A}"/>
+    <hyperlink ref="I23" r:id="rId45" location="page=8" xr:uid="{63BD0C7E-909D-4EE8-B058-1CAFDE653096}"/>
+    <hyperlink ref="I26" r:id="rId46" location="page=10" xr:uid="{BB0AD547-59AD-4708-B7C3-1F84822B759C}"/>
+    <hyperlink ref="I27" r:id="rId47" location="page=11" xr:uid="{DF2391A5-AFA5-4EA8-9B21-B0142AA4E39F}"/>
+    <hyperlink ref="I28" r:id="rId48" location="page=8" xr:uid="{E9F8F814-8FDC-4FFD-BD9D-37B758A1EE40}"/>
+    <hyperlink ref="I30" r:id="rId49" location="page=10" xr:uid="{67365D6C-9BED-4519-9B4D-5217F315DBD8}"/>
+    <hyperlink ref="I22" r:id="rId50" location="page=10" xr:uid="{D488CB2D-FA14-44B8-9738-68C7FE450972}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId36"/>
+  <legacyDrawing r:id="rId51"/>
 </worksheet>
 </file>
--- a/data/funds_master.xlsx
+++ b/data/funds_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harum\tsumitate-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4674585D-F775-4F02-AAAD-D11FED47ACB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796DCE66-CC64-4D67-B8A5-62AAEBE88A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="167">
   <si>
     <t>name</t>
   </si>
@@ -804,6 +804,14 @@
   </si>
   <si>
     <t>https://www.smtam.jp/fund/pdf/_id_510195_type_k.pdf#page=10</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.smd-am.co.jp/fund/pdf/154509k.pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>smds_pdf</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1426,7 +1434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="68.400000000000006">
+    <row r="4" spans="1:13" ht="68.400000000000006" hidden="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1464,7 +1472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="68.400000000000006">
+    <row r="5" spans="1:13" ht="68.400000000000006" hidden="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1502,7 +1510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="68.400000000000006">
+    <row r="6" spans="1:13" ht="68.400000000000006" hidden="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1540,7 +1548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="68.400000000000006" hidden="1">
+    <row r="7" spans="1:13" ht="68.400000000000006">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1568,8 +1576,8 @@
       <c r="I7" s="8"/>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
-      <c r="L7" t="b">
-        <v>0</v>
+      <c r="L7" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="42" hidden="1">
@@ -1610,7 +1618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="68.400000000000006">
+    <row r="9" spans="1:13" ht="68.400000000000006" hidden="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1724,7 +1732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="68.400000000000006">
+    <row r="12" spans="1:13" ht="68.400000000000006" hidden="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1902,7 +1910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="68.400000000000006" hidden="1">
+    <row r="17" spans="1:13" ht="68.400000000000006">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1930,11 +1938,11 @@
       <c r="I17" s="8"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
-      <c r="L17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="68.400000000000006">
+      <c r="L17" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="68.400000000000006" hidden="1">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2077,7 +2085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="55.2">
+    <row r="22" spans="1:13" ht="55.2" hidden="1">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2191,7 +2199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="42" hidden="1">
+    <row r="25" spans="1:13" ht="42">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2216,11 +2224,17 @@
       <c r="H25" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" t="b">
-        <v>0</v>
+      <c r="I25" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L25" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="42" hidden="1">
@@ -2337,7 +2351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="68.400000000000006">
+    <row r="29" spans="1:13" ht="68.400000000000006" hidden="1">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2413,7 +2427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="68.400000000000006">
+    <row r="31" spans="1:13" ht="68.400000000000006" hidden="1">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2458,9 +2472,9 @@
   <autoFilter ref="A1:F31" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="4">
       <filters>
-        <filter val="rakuten"/>
+        <filter val="daiwa"/>
         <filter val="sbi"/>
-        <filter val="smt"/>
+        <filter val="smds"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2525,8 +2539,9 @@
     <hyperlink ref="I28" r:id="rId48" location="page=8" xr:uid="{E9F8F814-8FDC-4FFD-BD9D-37B758A1EE40}"/>
     <hyperlink ref="I30" r:id="rId49" location="page=10" xr:uid="{67365D6C-9BED-4519-9B4D-5217F315DBD8}"/>
     <hyperlink ref="I22" r:id="rId50" location="page=10" xr:uid="{D488CB2D-FA14-44B8-9738-68C7FE450972}"/>
+    <hyperlink ref="I25" r:id="rId51" xr:uid="{706581E0-049E-4D80-8336-11A2E424069F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId51"/>
+  <legacyDrawing r:id="rId52"/>
 </worksheet>
 </file>
--- a/data/funds_master.xlsx
+++ b/data/funds_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harum\tsumitate-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796DCE66-CC64-4D67-B8A5-62AAEBE88A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9843DA-29B1-420C-BC59-D7F8AA81B69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="181">
   <si>
     <t>name</t>
   </si>
@@ -812,6 +812,68 @@
   </si>
   <si>
     <t>smds_pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.daiwa-am.co.jp/funds/doc_open/fund_doc_open.php?code=3346&amp;type=1&amp;preview=on</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.daiwa-am.co.jp/funds/doc_open/fund_doc_open.php?code=3340&amp;type=1&amp;preview=on</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am-one.co.jp/fund/pdf/313122/313122_mr.pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>amone_pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>管理費用は最新の月次レポートより</t>
+    <rPh sb="0" eb="4">
+      <t>カンリヒヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.am-one.co.jp/fund/pdf/313125/313125_mr.pdf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://toushin-lib.fwg.ne.jp/FdsWeb/FDST030000?isinCd=JP90C000D3K0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>capital_html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://www.resona-am.co.jp/fund/123015/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>resona_html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>管理費用：入口は HTML、本体は PDF</t>
+    <rPh sb="0" eb="4">
+      <t>カンリヒヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>manual</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>daiwa_manual</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1548,7 +1610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="68.400000000000006">
+    <row r="7" spans="1:13" ht="81.599999999999994">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1573,9 +1635,15 @@
       <c r="H7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
+      <c r="I7" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="L7" s="11" t="b">
         <v>1</v>
       </c>
@@ -1808,7 +1876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="55.2" hidden="1">
+    <row r="14" spans="1:13" ht="55.2">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1833,14 +1901,23 @@
       <c r="H14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="55.2" hidden="1">
+      <c r="I14" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="L14" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="55.2">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1865,11 +1942,20 @@
       <c r="H15" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" t="b">
-        <v>0</v>
+      <c r="I15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="L15" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="42" hidden="1">
@@ -1910,7 +1996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="68.400000000000006">
+    <row r="17" spans="1:13" ht="81.599999999999994">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1935,9 +2021,15 @@
       <c r="H17" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
+      <c r="I17" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="L17" s="11" t="b">
         <v>1</v>
       </c>
@@ -1983,7 +2075,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="55.2" hidden="1">
+    <row r="19" spans="1:13" ht="55.2">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2008,11 +2100,17 @@
       <c r="H19" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" t="b">
-        <v>0</v>
+      <c r="I19" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="L19" s="11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="42" hidden="1">
@@ -2053,7 +2151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="55.2" hidden="1">
+    <row r="21" spans="1:13" ht="55.2">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2078,11 +2176,20 @@
       <c r="H21" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" t="b">
-        <v>0</v>
+      <c r="I21" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="L21" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="55.2" hidden="1">
@@ -2472,7 +2579,10 @@
   <autoFilter ref="A1:F31" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="4">
       <filters>
+        <filter val="amone"/>
+        <filter val="capital"/>
         <filter val="daiwa"/>
+        <filter val="resona"/>
         <filter val="sbi"/>
         <filter val="smds"/>
       </filters>
@@ -2540,8 +2650,14 @@
     <hyperlink ref="I30" r:id="rId49" location="page=10" xr:uid="{67365D6C-9BED-4519-9B4D-5217F315DBD8}"/>
     <hyperlink ref="I22" r:id="rId50" location="page=10" xr:uid="{D488CB2D-FA14-44B8-9738-68C7FE450972}"/>
     <hyperlink ref="I25" r:id="rId51" xr:uid="{706581E0-049E-4D80-8336-11A2E424069F}"/>
+    <hyperlink ref="I7" r:id="rId52" xr:uid="{552897FF-4AA9-441A-A5B5-61C3A6E8B872}"/>
+    <hyperlink ref="I17" r:id="rId53" xr:uid="{A38704E5-797E-4C26-BC96-352859599DA4}"/>
+    <hyperlink ref="I14" r:id="rId54" xr:uid="{27512055-3BCF-42E6-869F-41203C727F8F}"/>
+    <hyperlink ref="I15" r:id="rId55" xr:uid="{3F36203C-960C-470B-AA83-2D24D1624E03}"/>
+    <hyperlink ref="I19" r:id="rId56" xr:uid="{0166EDFB-5EB3-40E5-B975-047C7A7A3A50}"/>
+    <hyperlink ref="I21" r:id="rId57" xr:uid="{3E8613BB-A8CA-4D98-A187-48E6F9E4AEA0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId52"/>
+  <legacyDrawing r:id="rId58"/>
 </worksheet>
 </file>
--- a/data/funds_master.xlsx
+++ b/data/funds_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harum\tsumitate-app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD9843DA-29B1-420C-BC59-D7F8AA81B69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27DFD34-B05F-4E3C-8D2D-3E7B682BB374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1645,7 +1645,7 @@
         <v>180</v>
       </c>
       <c r="L7" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="42" hidden="1">
@@ -2031,7 +2031,7 @@
         <v>180</v>
       </c>
       <c r="L17" s="11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="68.400000000000006" hidden="1">
